--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.73574075340966</v>
+        <v>9.86955787242907</v>
       </c>
       <c r="D2" t="n">
-        <v>46.04118140846875</v>
+        <v>7.481691978876173</v>
       </c>
       <c r="E2" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F2" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.17607777880869</v>
+        <v>10.10361263905641</v>
       </c>
       <c r="D3" t="n">
-        <v>39.29691499780449</v>
+        <v>6.38574868714323</v>
       </c>
       <c r="E3" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F3" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>93.79167874026291</v>
+        <v>15.24114779529272</v>
       </c>
       <c r="D4" t="n">
-        <v>24.07504308030942</v>
+        <v>3.91219450055028</v>
       </c>
       <c r="E4" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F4" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>66.31500567084527</v>
+        <v>10.77618842151236</v>
       </c>
       <c r="D5" t="n">
-        <v>18.36624255412898</v>
+        <v>2.984514415045959</v>
       </c>
       <c r="E5" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F5" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.27517723031594</v>
+        <v>9.14471629992634</v>
       </c>
       <c r="D6" t="n">
-        <v>20.00142625299993</v>
+        <v>3.250231766112489</v>
       </c>
       <c r="E6" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F6" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.52521842416948</v>
+        <v>6.910347993927541</v>
       </c>
       <c r="D7" t="n">
-        <v>45.13414042397489</v>
+        <v>7.33429781889592</v>
       </c>
       <c r="E7" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F7" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>75.37047703846741</v>
+        <v>12.24770251875096</v>
       </c>
       <c r="D8" t="n">
-        <v>4.239118349505404</v>
+        <v>0.6888567317946281</v>
       </c>
       <c r="E8" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F8" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.42454564825271</v>
+        <v>7.706488667841065</v>
       </c>
       <c r="D9" t="n">
-        <v>13.47647850556396</v>
+        <v>2.189927757154144</v>
       </c>
       <c r="E9" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F9" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.37290231762508</v>
+        <v>8.348096626614076</v>
       </c>
       <c r="D10" t="n">
-        <v>6.415678253807786</v>
+        <v>1.042547716243765</v>
       </c>
       <c r="E10" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F10" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.45804460607619</v>
+        <v>5.761932248487382</v>
       </c>
       <c r="D11" t="n">
-        <v>10.88339951394875</v>
+        <v>1.768552421016671</v>
       </c>
       <c r="E11" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F11" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.61885259365527</v>
+        <v>6.925563546468982</v>
       </c>
       <c r="D12" t="n">
-        <v>29.75634826155537</v>
+        <v>4.835406592502748</v>
       </c>
       <c r="E12" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F12" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>53.29473298472016</v>
+        <v>8.660394110017027</v>
       </c>
       <c r="D13" t="n">
-        <v>17.9243448855905</v>
+        <v>2.912706043908456</v>
       </c>
       <c r="E13" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F13" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.65733465549042</v>
+        <v>5.306816881517194</v>
       </c>
       <c r="D14" t="n">
-        <v>19.86626545715016</v>
+        <v>3.2282681367869</v>
       </c>
       <c r="E14" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F14" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.06726882498436</v>
+        <v>6.510931184059959</v>
       </c>
       <c r="D15" t="n">
-        <v>19.01081080481266</v>
+        <v>3.089256755782058</v>
       </c>
       <c r="E15" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F15" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1170701101539</v>
+        <v>3.756523892900009</v>
       </c>
       <c r="D16" t="n">
-        <v>16.60719423927118</v>
+        <v>2.698669063881566</v>
       </c>
       <c r="E16" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F16" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>53.16663315341925</v>
+        <v>8.639577887430628</v>
       </c>
       <c r="D17" t="n">
-        <v>30.2076804432153</v>
+        <v>4.908748072022487</v>
       </c>
       <c r="E17" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F17" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.92418524764197</v>
+        <v>4.86268010274182</v>
       </c>
       <c r="D18" t="n">
-        <v>23.4023152977901</v>
+        <v>3.802876235890892</v>
       </c>
       <c r="E18" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F18" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>35.030978504783</v>
+        <v>5.692534007027238</v>
       </c>
       <c r="D19" t="n">
-        <v>35.25759176667106</v>
+        <v>5.729358662084047</v>
       </c>
       <c r="E19" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F19" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>37.69854004201991</v>
+        <v>6.126012756828235</v>
       </c>
       <c r="D20" t="n">
-        <v>33.21881546970991</v>
+        <v>5.398057513827861</v>
       </c>
       <c r="E20" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F20" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>44.03091157982142</v>
+        <v>7.155023131720981</v>
       </c>
       <c r="D21" t="n">
-        <v>16.85306314711882</v>
+        <v>2.738622761406808</v>
       </c>
       <c r="E21" t="n">
-        <v>16.43698193659007</v>
+        <v>2.671009564695886</v>
       </c>
       <c r="F21" t="n">
-        <v>11.53276373120639</v>
+        <v>1.874074106321039</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
